--- a/ssd/ssd.xlsx
+++ b/ssd/ssd.xlsx
@@ -106,7 +106,7 @@
     <t xml:space="preserve">github.com/LSSTDESC/grb_orphan_afterglows</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3</t>
+    <t xml:space="preserve">1.0</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
